--- a/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
@@ -826,8 +826,8 @@
         <v>58.328061247499996</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. En el servicio de catering todo va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992, alcohol incluido); el alcohol que sale por drop-off y el pan común, si los tienes, mueven la media. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.","")</f>
-        <v>Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: 10 %. En el servicio de catering todo va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992, alcohol incluido); el alcohol que sale por drop-off y el pan común, si los tienes, mueven la media. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.</v>
+        <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. En el servicio de catering todo va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992, alcohol incluido); el alcohol que sale por drop-off mueve la media. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.","")</f>
+        <v>Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: 10 %. En el servicio de catering todo va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992, alcohol incluido); el alcohol que sale por drop-off mueve la media. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.</v>
       </c>
     </row>
     <row r="10">
@@ -924,7 +924,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Parte de las ventas que se entrega SIN servicio (drop-off: bandejas de coffee break o de almuerzo que se dejan en la oficina). Es entrega de bienes: la comida va al 10 % y el alcohol y los refrescos con azúcar añadido, al 21 %, y así lo aplica el libro a esta parte</t>
+          <t>Parte de las ventas que se entrega SIN servicio (drop-off: bandejas de coffee break o de almuerzo que se dejan en la oficina). Es entrega de bienes: la comida va al 10 % y el alcohol y los refrescos, zumos y gaseosas con azúcares o edulcorantes añadidos, al 21 % (art. 91.Uno.1.1.º de la Ley 37/1992); el libro lo aplica al alcohol de esta parte</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tres meses de costes fijos: cubren un invierno flojo (enero y febrero son los meses más bajos del año) y los 30-60 días que tardan en pagar las empresas</t>
+          <t>Tres meses de costes fijos: cubren los meses flojos (enero y agosto son los más bajos del año) y los 30-60 días que tardan en pagar las empresas</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tipo general. En este libro lo usan dos cosas: el IVA que soportas al comprar el alcohol (el proveedor lo factura al 21 %) y el que repercutes por el alcohol que sale por drop-off (es una entrega de bienes). El alcohol servido en el servicio de catering va al reducido: su tipo está en el bloque de desglose del IVA. Suministros, equipamiento y servicios tienen su tipo en la celda de abajo. El libro manda al general sólo el alcohol: si compras refrescos o zumos con azúcares añadidos, su factura también va al 21 % (art. 91.Uno.1.1.º de la Ley 37/1992)</t>
+          <t>Tipo general. En este libro lo usan dos cosas: el IVA que soportas al comprar el alcohol (el proveedor lo factura al 21 %) y el que repercutes por el alcohol que sale por drop-off (es una entrega de bienes). El alcohol servido en el servicio de catering va al reducido: su tipo está en el bloque de desglose del IVA. Suministros, equipamiento y servicios tienen su tipo en la celda de abajo. El libro manda al general sólo el alcohol: si compras refrescos, zumos y gaseosas con azúcares o edulcorantes añadidos, su factura también va al 21 % (art. 91.Uno.1.1.º de la Ley 37/1992)</t>
         </is>
       </c>
     </row>
@@ -2107,8 +2107,8 @@
         <v>0.015341510460685614</v>
       </c>
       <c r="D22" s="28" t="str">
-        <f>IFERROR("Renta "&amp;IF('0. Supuestos'!$B$54=1,"del mes","de los "&amp;TEXT('0. Supuestos'!$B$54,"0")&amp;" meses")&amp;" de obra y licencias. NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación","")</f>
-        <v>Renta del mes de obra y licencias. NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación</v>
+        <f>IFERROR("Renta "&amp;IF('0. Supuestos'!$B$54=1,"del mes","de los "&amp;TEXT('0. Supuestos'!$B$54,"0")&amp;" meses")&amp;" de puesta en marcha (pruebas de menú y degustaciones). NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación","")</f>
+        <v>Renta del mes de puesta en marcha (pruebas de menú y degustaciones). NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación</v>
       </c>
       <c r="E22" s="28" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="23">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>Imprevistos de obra y acondicionamiento</t>
+          <t>Imprevistos de la compra y preparación de la furgoneta</t>
         </is>
       </c>
       <c r="B23" s="32">
@@ -2131,8 +2131,8 @@
         <v>0.014421019833044477</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
-        <v>Al 8% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <v>Al 8% de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
       <c r="I19" s="28" t="n"/>
       <c r="J19" s="28" t="inlineStr">
         <is>
-          <t>Personas trabajando a la vez en un evento medio de 65 invitados: los cuatro fijos y cuatro del equipo de evento. Una boda de 110 pide más: súbelo y la hoja te dice si llega la plantilla</t>
+          <t>Personas trabajando a la vez en un evento medio de 65 invitados: los tres fijos a jornada completa, la coordinadora y cuatro extras. Una boda de 110 pide más: súbelo y la hoja te dice si llega la plantilla</t>
         </is>
       </c>
     </row>
@@ -6220,10 +6220,10 @@
       <c r="D7" s="28" t="n"/>
       <c r="E7" s="28" t="n"/>
     </row>
-    <row r="8" ht="225" customHeight="1">
+    <row r="8" ht="210" customHeight="1">
       <c r="A8" s="46" t="inlineStr">
         <is>
-          <t>4. Todas las cifras van SIN IVA. Para pasar un PVP a precio sin IVA, divide por el tipo que le corresponda: entre 1,10 en el servicio de catering (comida y bebida, alcohol incluido: art. 91.Uno.2.2.º de la Ley 37/1992 del IVA) y, cuando se venden para llevar, los alimentos —bollería y pastelería incluidas—, que son productos alimenticios al tipo reducido por el art. 91.Uno.1.1.º; y entre 1,21 el tipo general, que en hostelería sólo alcanza a lo que sale de la cocina central como entrega de bienes excluida del reducido: el alcohol y los refrescos o zumos con azúcares añadidos para llevar o a domicilio (la comida para llevar sigue al 10 %); el libro lo aplica al alcohol del canal de drop-off. El tipo de cada línea de venta está en la columna «Tipo de IVA de la línea» del P&amp;L y de ahí salen los cobros, el IVA repercutido y el PVP equivalente. El IVA de la inversión se adelanta y se recupera con el modelo 303.</t>
+          <t>4. Todas las cifras van SIN IVA. Para pasar un PVP a precio sin IVA, divide por el tipo que le corresponda: entre 1,10 en el servicio de catering (comida y bebida, alcohol incluido: art. 91.Uno.2.2.º de la Ley 37/1992 del IVA) y, cuando se venden para llevar, los alimentos, que son productos alimenticios al tipo reducido por el art. 91.Uno.1.1.º; y entre 1,21 el tipo general, que en hostelería sólo alcanza a lo que sale de la cocina central como entrega de bienes excluida del reducido: el alcohol y los refrescos, zumos y gaseosas con azúcares o edulcorantes añadidos para llevar o a domicilio (la comida para llevar sigue al 10 %); el libro lo aplica al alcohol del canal de drop-off. El tipo de cada línea de venta está en la columna «Tipo de IVA de la línea» del P&amp;L y de ahí salen los cobros, el IVA repercutido y el PVP equivalente. El IVA de la inversión se adelanta y se recupera con el modelo 303.</t>
         </is>
       </c>
       <c r="B8" s="28" t="n"/>

--- a/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
@@ -8527,7 +8527,7 @@
       <c r="C31" s="28" t="n"/>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>Mide cuánto tarda el negocio en devolver la inversión con lo que genera ANTES de pagar al banco, con la MISMA base de flujo en los tres años; si puedes pagar la cuota lo dice el DSCR de la hoja de Financiación. El documento Word del pack sigue en la versión 1.1 y no lee esta celda: las cifras válidas son las de este libro</t>
+          <t>Mide cuánto tarda el negocio en devolver la inversión con lo que genera ANTES de pagar al banco, con la MISMA base de flujo en los tres años; si puedes pagar la cuota lo dice el DSCR de la hoja de Financiación. El plan de negocio en Word cita esta cifra; si cambias una celda verde, manda este libro</t>
         </is>
       </c>
       <c r="E31" s="28" t="n"/>

--- a/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="B9" s="65">
         <f>IFERROR(IF($B$5="","",$B$5*(1+SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))),"")</f>
-        <v>58.328061247499996</v>
+        <v>58.33410550000001</v>
       </c>
       <c r="C9" t="str">
         <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. En el servicio de catering todo va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992, alcohol incluido); el alcohol que sale por drop-off mueve la media. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.","")</f>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="B11" s="64" t="n">
-        <v>0.8519</v>
+        <v>0.82</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="B12" s="66">
         <f>IFERROR(IF(COUNT(B11)=0,"",1-B11),"")</f>
-        <v>0.1481</v>
+        <v>0.18000000000000005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2541,19 +2541,19 @@
       </c>
       <c r="B10" s="32">
         <f>IFERROR(IF(B9="","",B9*$E$10),"")</f>
-        <v>381523.415</v>
+        <v>367237.0</v>
       </c>
       <c r="C10" s="32">
         <f>IFERROR(IF(C9="","",C9*$E$10),"")</f>
-        <v>427306.2248</v>
+        <v>411305.44</v>
       </c>
       <c r="D10" s="32">
         <f>IFERROR(IF(D9="","",D9*$E$10),"")</f>
-        <v>461490.7227840001</v>
+        <v>444209.87520000007</v>
       </c>
       <c r="E10" s="68">
         <f>IFERROR(IF('0. Supuestos'!$B$11="","",'0. Supuestos'!$B$11),"")</f>
-        <v>0.8519</v>
+        <v>0.82</v>
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
@@ -2574,19 +2574,19 @@
       </c>
       <c r="B11" s="32">
         <f>IFERROR(IF(B9="","",B9*$E$11),"")</f>
-        <v>66326.585</v>
+        <v>80613.00000000003</v>
       </c>
       <c r="C11" s="32">
         <f>IFERROR(IF(C9="","",C9*$E$11),"")</f>
-        <v>74285.77520000002</v>
+        <v>90286.56000000004</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR(IF(D9="","",D9*$E$11),"")</f>
-        <v>80228.63721600002</v>
+        <v>97509.48480000005</v>
       </c>
       <c r="E11" s="68">
         <f>IFERROR(IF('0. Supuestos'!$B$12="","",'0. Supuestos'!$B$12),"")</f>
-        <v>0.1481</v>
+        <v>0.18000000000000005</v>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
@@ -2621,19 +2621,19 @@
       </c>
       <c r="B13" s="32">
         <f>IFERROR(IF(B9="","",B9*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>114457.02449999998</v>
+        <v>110171.09999999999</v>
       </c>
       <c r="C13" s="32">
         <f>IFERROR(IF(C9="","",C9*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>128191.86744</v>
+        <v>123391.632</v>
       </c>
       <c r="D13" s="32">
         <f>IFERROR(IF(D9="","",D9*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>138447.21683520003</v>
+        <v>133262.96256</v>
       </c>
       <c r="E13" s="68">
         <f>IFERROR(B13/$B$9,"")</f>
-        <v>0.25556999999999996</v>
+        <v>0.24599999999999997</v>
       </c>
       <c r="F13" s="28" t="str">
         <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea","")</f>
@@ -2653,19 +2653,19 @@
       </c>
       <c r="B14" s="32">
         <f>IFERROR(IF(B9="","",B9*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>18571.443800000005</v>
+        <v>22571.64000000001</v>
       </c>
       <c r="C14" s="32">
         <f>IFERROR(IF(C9="","",C9*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>20800.017056000008</v>
+        <v>25280.236800000013</v>
       </c>
       <c r="D14" s="32">
         <f>IFERROR(IF(D9="","",D9*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>22464.018420480006</v>
+        <v>27302.655744000018</v>
       </c>
       <c r="E14" s="68">
         <f>IFERROR(B14/$B$9,"")</f>
-        <v>0.04146800000000001</v>
+        <v>0.05040000000000002</v>
       </c>
       <c r="F14" s="28" t="str">
         <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$14,"0%")&amp;" de las ventas de BEBIDA","")</f>
@@ -2811,19 +2811,19 @@
       </c>
       <c r="B19" s="26">
         <f>IFERROR(IF(B9="","",SUM(B13:B18)),"")</f>
-        <v>173334.96829999998</v>
+        <v>173049.24</v>
       </c>
       <c r="C19" s="26">
         <f>IFERROR(IF(C9="","",SUM(C13:C18)),"")</f>
-        <v>194135.164496</v>
+        <v>193815.14880000002</v>
       </c>
       <c r="D19" s="26">
         <f>IFERROR(IF(D9="","",SUM(D13:D18)),"")</f>
-        <v>209665.97765568004</v>
+        <v>209320.36070400005</v>
       </c>
       <c r="E19" s="67">
         <f>IFERROR(B19/$B$9,"")</f>
-        <v>0.38703799999999994</v>
+        <v>0.38639999999999997</v>
       </c>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
@@ -2837,19 +2837,19 @@
       </c>
       <c r="B20" s="26">
         <f>IFERROR(IF(B9="","",B9-B19),"")</f>
-        <v>274515.03170000005</v>
+        <v>274800.76</v>
       </c>
       <c r="C20" s="26">
         <f>IFERROR(IF(C9="","",C9-C19),"")</f>
-        <v>307456.8355040001</v>
+        <v>307776.85120000003</v>
       </c>
       <c r="D20" s="26">
         <f>IFERROR(IF(D9="","",D9-D19),"")</f>
-        <v>332053.38234432007</v>
+        <v>332398.99929600005</v>
       </c>
       <c r="E20" s="67">
         <f>IFERROR(B20/$B$9,"")</f>
-        <v>0.6129620000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="F20" s="28" t="n"/>
       <c r="G20" s="28" t="n"/>
@@ -3417,15 +3417,15 @@
       </c>
       <c r="B39" s="32">
         <f>IFERROR(IF(B9="","",SUMPRODUCT(B13:B18,G13:G18)),"")</f>
-        <v>22624.8275617</v>
+        <v>22882.268760000003</v>
       </c>
       <c r="C39" s="32">
         <f>IFERROR(IF(C9="","",SUMPRODUCT(C13:C18,G13:G18)),"")</f>
-        <v>25339.806869104006</v>
+        <v>25628.14101120001</v>
       </c>
       <c r="D39" s="32">
         <f>IFERROR(IF(D9="","",SUMPRODUCT(D13:D18,G13:G18)),"")</f>
-        <v>27366.99141863233</v>
+        <v>27678.39229209601</v>
       </c>
       <c r="E39" s="28" t="n"/>
       <c r="F39" s="28" t="inlineStr">
@@ -3467,19 +3467,19 @@
       </c>
       <c r="B41" s="26">
         <f>IFERROR(IF(B9="","",B20-B38),"")</f>
-        <v>46231.49170000004</v>
+        <v>46517.22</v>
       </c>
       <c r="C41" s="26">
         <f>IFERROR(IF(C9="","",C20-C38),"")</f>
-        <v>73173.29550400007</v>
+        <v>73493.31120000003</v>
       </c>
       <c r="D41" s="26">
         <f>IFERROR(IF(D9="","",D20-D38),"")</f>
-        <v>93037.04553308594</v>
+        <v>93382.66248476593</v>
       </c>
       <c r="E41" s="67">
         <f>IFERROR(B41/$B$9,"")</f>
-        <v>0.10322985754158769</v>
+        <v>0.10386785754158759</v>
       </c>
       <c r="F41" s="28" t="n"/>
       <c r="G41" s="28" t="n"/>
@@ -3520,15 +3520,15 @@
       </c>
       <c r="B43" s="32">
         <f>IFERROR(IF(B9="","",MAX(0,B41-B42)),"")</f>
-        <v>46231.49170000004</v>
+        <v>46517.22</v>
       </c>
       <c r="C43" s="32">
         <f>IFERROR(IF(C9="","",MAX(0,C41-C42)),"")</f>
-        <v>73173.29550400007</v>
+        <v>73493.31120000003</v>
       </c>
       <c r="D43" s="32">
         <f>IFERROR(IF(D9="","",MAX(0,D41-D42)),"")</f>
-        <v>93037.04553308594</v>
+        <v>93382.66248476593</v>
       </c>
       <c r="E43" s="28" t="n"/>
       <c r="F43" s="28" t="n"/>
@@ -3593,15 +3593,15 @@
       </c>
       <c r="B46" s="32">
         <f>IFERROR(IF(B9="","",IF(B45="",0,B43*B45)),"")</f>
-        <v>6934.723755000006</v>
+        <v>6977.583</v>
       </c>
       <c r="C46" s="32">
         <f>IFERROR(IF(C9="","",IF(C45="",0,C43*C45)),"")</f>
-        <v>10975.99432560001</v>
+        <v>11023.996680000004</v>
       </c>
       <c r="D46" s="32">
         <f>IFERROR(IF(D9="","",IF(D45="",0,D43*D45)),"")</f>
-        <v>23259.261383271485</v>
+        <v>23345.66562119148</v>
       </c>
       <c r="E46" s="28" t="n"/>
       <c r="F46" s="28" t="n"/>
@@ -3639,19 +3639,19 @@
       </c>
       <c r="B48" s="26">
         <f>IFERROR(IF(B9="","",B41-B46),"")</f>
-        <v>39296.767945000036</v>
+        <v>39539.637</v>
       </c>
       <c r="C48" s="26">
         <f>IFERROR(IF(C9="","",C41-C46),"")</f>
-        <v>62197.301178400056</v>
+        <v>62469.31452000002</v>
       </c>
       <c r="D48" s="26">
         <f>IFERROR(IF(D9="","",D41-D46),"")</f>
-        <v>69777.78414981446</v>
+        <v>70036.99686357444</v>
       </c>
       <c r="E48" s="67">
         <f>IFERROR(B48/$B$9,"")</f>
-        <v>0.08774537891034953</v>
+        <v>0.08828767891034946</v>
       </c>
       <c r="F48" s="28" t="n"/>
       <c r="G48" s="28" t="n"/>
@@ -3713,15 +3713,15 @@
       </c>
       <c r="B51" s="68">
         <f>IFERROR(IF(B9="","",B20/B9),"")</f>
-        <v>0.6129620000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="C51" s="68">
         <f>IFERROR(IF(C9="","",C20/C9),"")</f>
-        <v>0.6129620000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="D51" s="68">
         <f>IFERROR(IF(D9="","",D20/D9),"")</f>
-        <v>0.612962</v>
+        <v>0.6136</v>
       </c>
       <c r="E51" s="75" t="n">
         <v>0.6</v>
@@ -3742,15 +3742,15 @@
       </c>
       <c r="B52" s="32">
         <f>IFERROR(IF(B9="","",B13+B14),"")</f>
-        <v>133028.46829999998</v>
+        <v>132742.74</v>
       </c>
       <c r="C52" s="32">
         <f>IFERROR(IF(C9="","",C13+C14),"")</f>
-        <v>148991.884496</v>
+        <v>148671.8688</v>
       </c>
       <c r="D52" s="32">
         <f>IFERROR(IF(D9="","",D13+D14),"")</f>
-        <v>160911.23525568005</v>
+        <v>160565.61830400003</v>
       </c>
       <c r="E52" s="28" t="n"/>
       <c r="F52" s="28" t="n"/>
@@ -3765,15 +3765,15 @@
       </c>
       <c r="B53" s="68">
         <f>IFERROR(IF(B9="","",B52/B9),"")</f>
-        <v>0.29703799999999997</v>
+        <v>0.2964</v>
       </c>
       <c r="C53" s="68">
         <f>IFERROR(IF(C9="","",C52/C9),"")</f>
-        <v>0.29703799999999997</v>
+        <v>0.29639999999999994</v>
       </c>
       <c r="D53" s="68">
         <f>IFERROR(IF(D9="","",D52/D9),"")</f>
-        <v>0.297038</v>
+        <v>0.2964</v>
       </c>
       <c r="E53" s="75" t="n">
         <v>0.33</v>
@@ -3852,15 +3852,15 @@
       </c>
       <c r="B56" s="68">
         <f>IFERROR(IF(B9="","",B48/B9),"")</f>
-        <v>0.08774537891034953</v>
+        <v>0.08828767891034946</v>
       </c>
       <c r="C56" s="68">
         <f>IFERROR(IF(C9="","",C48/C9),"")</f>
-        <v>0.12399978703488103</v>
+        <v>0.12454208703488097</v>
       </c>
       <c r="D56" s="68">
         <f>IFERROR(IF(D9="","",D48/D9),"")</f>
-        <v>0.12880799414260263</v>
+        <v>0.1292864941426026</v>
       </c>
       <c r="E56" s="75" t="n">
         <v>0.04</v>
@@ -4170,15 +4170,15 @@
       </c>
       <c r="B9" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$19/('PyG 3 Años'!$B$6*'PyG 3 Años'!$B$8)),"")</f>
-        <v>20.513014</v>
+        <v>20.4792</v>
       </c>
       <c r="C9" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",'PyG 3 Años'!$C$19/('PyG 3 Años'!$C$6*'PyG 3 Años'!$C$8)),"")</f>
-        <v>20.513014</v>
+        <v>20.4792</v>
       </c>
       <c r="D9" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",'PyG 3 Años'!$D$19/('PyG 3 Años'!$D$6*'PyG 3 Años'!$D$8)),"")</f>
-        <v>20.513014</v>
+        <v>20.4792</v>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
@@ -4195,15 +4195,15 @@
       </c>
       <c r="B10" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B8-B9),"")</f>
-        <v>32.486986</v>
+        <v>32.5208</v>
       </c>
       <c r="C10" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C8-C9),"")</f>
-        <v>32.486986</v>
+        <v>32.5208</v>
       </c>
       <c r="D10" s="70">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D8-D9),"")</f>
-        <v>32.486986</v>
+        <v>32.5208</v>
       </c>
       <c r="E10" s="28" t="inlineStr">
         <is>
@@ -4282,15 +4282,15 @@
       </c>
       <c r="B14" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",IF(B10&lt;=0,"",B6/B10)),"")</f>
-        <v>7026.922719146676</v>
+        <v>7019.616368601019</v>
       </c>
       <c r="C14" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",IF(C10&lt;=0,"",C6/C10)),"")</f>
-        <v>7211.61205905651</v>
+        <v>7204.113674940346</v>
       </c>
       <c r="D14" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",IF(D10&lt;=0,"",D6/D10)),"")</f>
-        <v>7357.294912222208</v>
+        <v>7349.645052127688</v>
       </c>
       <c r="E14" s="28" t="n"/>
       <c r="F14" s="28" t="n"/>
@@ -4303,15 +4303,15 @@
       </c>
       <c r="B15" s="44">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B14/B11),"")</f>
-        <v>54.05325168574366</v>
+        <v>53.99704898923861</v>
       </c>
       <c r="C15" s="44">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C14/C11),"")</f>
-        <v>55.4739389158193</v>
+        <v>55.41625903800266</v>
       </c>
       <c r="D15" s="44">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D14/D11),"")</f>
-        <v>56.59457624786314</v>
+        <v>56.53573117021299</v>
       </c>
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
@@ -4324,15 +4324,15 @@
       </c>
       <c r="B16" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B14*B8),"")</f>
-        <v>372426.90411477385</v>
+        <v>372039.667535854</v>
       </c>
       <c r="C16" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C14*C8),"")</f>
-        <v>382215.439129995</v>
+        <v>381818.02477183833</v>
       </c>
       <c r="D16" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D14*D8),"")</f>
-        <v>389936.63034777704</v>
+        <v>389531.1877627675</v>
       </c>
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
@@ -4382,15 +4382,15 @@
       </c>
       <c r="B19" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",IF(B10&lt;=0,"",B18/B10)),"")</f>
-        <v>6831.690696083656</v>
+        <v>6824.587341024821</v>
       </c>
       <c r="C19" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",IF(C10&lt;=0,"",C18/C10)),"")</f>
-        <v>7616.47983205709</v>
+        <v>7608.560480471607</v>
       </c>
       <c r="D19" s="40">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",IF(D10&lt;=0,"",D18/D10)),"")</f>
-        <v>7801.169171966923</v>
+        <v>7793.057786810934</v>
       </c>
       <c r="E19" s="28" t="n"/>
       <c r="F19" s="28" t="n"/>
@@ -4403,15 +4403,15 @@
       </c>
       <c r="B20" s="45">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B19/B11),"")</f>
-        <v>52.5514668929512</v>
+        <v>52.49682570019093</v>
       </c>
       <c r="C20" s="45">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C19/C11),"")</f>
-        <v>58.58830640043915</v>
+        <v>58.52738831132005</v>
       </c>
       <c r="D20" s="45">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D19/D11),"")</f>
-        <v>60.008993630514794</v>
+        <v>59.94659836008411</v>
       </c>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
@@ -4424,15 +4424,15 @@
       </c>
       <c r="B21" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B19*B8),"")</f>
-        <v>362079.6068924338</v>
+        <v>361703.12907431554</v>
       </c>
       <c r="C21" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C19*C8),"")</f>
-        <v>403673.43109902577</v>
+        <v>403253.7054649952</v>
       </c>
       <c r="D21" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D19*D8),"")</f>
-        <v>413461.9661142469</v>
+        <v>413032.0627009795</v>
       </c>
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
@@ -4478,15 +4478,15 @@
       </c>
       <c r="B24" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B23/B20-1),"")</f>
-        <v>0.23688269506171555</v>
+        <v>0.23817010139269423</v>
       </c>
       <c r="C24" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$C$9="","",C23/C20-1),"")</f>
-        <v>0.24256877306585434</v>
+        <v>0.24386209773723033</v>
       </c>
       <c r="D24" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$D$9="","",D23/D20-1),"")</f>
-        <v>0.3102036085474267</v>
+        <v>0.3115673307720559</v>
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
     <row r="26" ht="46" customHeight="1">
       <c r="A26" s="28" t="str">
         <f>IFERROR("Con el precio medio por invitado sin IVA de la fila de arriba necesitas "&amp;TEXT(ROUNDUP(B15,0),"0")&amp;" invitados por evento durante los "&amp;TEXT(B11,"0")&amp;" eventos del año para no perder dinero (equilibrio contable, con la amortización dentro), y "&amp;TEXT(ROUNDUP(B20,0),"0")&amp;" para que la caja aguante (equilibrio de caja: sin la amortización, que no se paga, y con la cuota del préstamo del año"&amp;IF(B12=0,"; este año sólo intereses, porque el préstamo está en carencia","")&amp;"). En las filas «Ingresos necesarios al año» tienes esas mismas cifras en euros.","")</f>
-        <v>Con el precio medio por invitado sin IVA de la fila de arriba necesitas 55 invitados por evento durante los 130 eventos del año para no perder dinero (equilibrio contable, con la amortización dentro), y 53 para que la caja aguante (equilibrio de caja: sin la amortización, que no se paga, y con la cuota del préstamo del año; este año sólo intereses, porque el préstamo está en carencia). En las filas «Ingresos necesarios al año» tienes esas mismas cifras en euros.</v>
+        <v>Con el precio medio por invitado sin IVA de la fila de arriba necesitas 54 invitados por evento durante los 130 eventos del año para no perder dinero (equilibrio contable, con la amortización dentro), y 53 para que la caja aguante (equilibrio de caja: sin la amortización, que no se paga, y con la cuota del préstamo del año; este año sólo intereses, porque el préstamo está en carencia). En las filas «Ingresos necesarios al año» tienes esas mismas cifras en euros.</v>
       </c>
       <c r="B26" s="28" t="n"/>
       <c r="C26" s="28" t="n"/>
@@ -4585,115 +4585,115 @@
     <row r="32">
       <c r="A32" s="70">
         <f>IFERROR($B$9*0.85,"")</f>
-        <v>17.4360619</v>
+        <v>17.40732</v>
       </c>
       <c r="B32" s="44">
         <f>IFERROR(IF($B$31-$A32&lt;=0,"",$B$6/($B$31-$A32)/$B$11),"")</f>
-        <v>52.31886751600316</v>
+        <v>52.27410348829658</v>
       </c>
       <c r="C32" s="44">
         <f>IFERROR(IF($C$31-$A32&lt;=0,"",$B$6/($C$31-$A32)/$B$11),"")</f>
-        <v>49.37662487859382</v>
+        <v>49.336752129067854</v>
       </c>
       <c r="D32" s="44">
         <f>IFERROR(IF($D$31-$A32&lt;=0,"",$B$6/($D$31-$A32)/$B$11),"")</f>
-        <v>46.7476872657617</v>
+        <v>46.711945803524266</v>
       </c>
       <c r="E32" s="44">
         <f>IFERROR(IF($E$31-$A32&lt;=0,"",$B$6/($E$31-$A32)/$B$11),"")</f>
-        <v>44.38454095067019</v>
+        <v>44.35232044835638</v>
       </c>
       <c r="F32" s="28" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="70">
         <f>IFERROR($B$9*0.925,"")</f>
-        <v>18.97453795</v>
+        <v>18.94326</v>
       </c>
       <c r="B33" s="44">
         <f>IFERROR(IF($B$31-$A33&lt;=0,"",$B$6/($B$31-$A33)/$B$11),"")</f>
-        <v>54.83222156256855</v>
+        <v>54.778721441083235</v>
       </c>
       <c r="C33" s="44">
         <f>IFERROR(IF($C$31-$A33&lt;=0,"",$B$6/($C$31-$A33)/$B$11),"")</f>
-        <v>51.60921042567387</v>
+        <v>51.56181216314981</v>
       </c>
       <c r="D33" s="44">
         <f>IFERROR(IF($D$31-$A33&lt;=0,"",$B$6/($D$31-$A33)/$B$11),"")</f>
-        <v>48.74405853093648</v>
+        <v>48.70177477967311</v>
       </c>
       <c r="E33" s="44">
         <f>IFERROR(IF($E$31-$A33&lt;=0,"",$B$6/($E$31-$A33)/$B$11),"")</f>
-        <v>46.18029962292676</v>
+        <v>46.14234510809992</v>
       </c>
       <c r="F33" s="28" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="70">
         <f>IFERROR($B$9*1.0,"")</f>
-        <v>20.513014</v>
+        <v>20.4792</v>
       </c>
       <c r="B34" s="44">
         <f>IFERROR(IF($B$31-$A34&lt;=0,"",$B$6/($B$31-$A34)/$B$11),"")</f>
-        <v>57.59924023874419</v>
+        <v>57.53542602976432</v>
       </c>
       <c r="C34" s="44">
         <f>IFERROR(IF($C$31-$A34&lt;=0,"",$B$6/($C$31-$A34)/$B$11),"")</f>
-        <v>54.05325168574366</v>
+        <v>53.99704898923861</v>
       </c>
       <c r="D34" s="44">
         <f>IFERROR(IF($D$31-$A34&lt;=0,"",$B$6/($D$31-$A34)/$B$11),"")</f>
-        <v>50.91854738390971</v>
+        <v>50.86867137404784</v>
       </c>
       <c r="E34" s="44">
         <f>IFERROR(IF($E$31-$A34&lt;=0,"",$B$6/($E$31-$A34)/$B$11),"")</f>
-        <v>48.127494848964254</v>
+        <v>48.08293440366123</v>
       </c>
       <c r="F34" s="28" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="70">
         <f>IFERROR($B$9*1.075,"")</f>
-        <v>22.051490049999998</v>
+        <v>22.01514</v>
       </c>
       <c r="B35" s="44">
         <f>IFERROR(IF($B$31-$A35&lt;=0,"",$B$6/($B$31-$A35)/$B$11),"")</f>
-        <v>60.66036676161395</v>
+        <v>60.58429230878571</v>
       </c>
       <c r="C35" s="44">
         <f>IFERROR(IF($C$31-$A35&lt;=0,"",$B$6/($C$31-$A35)/$B$11),"")</f>
-        <v>56.740283574435246</v>
+        <v>56.67371841503337</v>
       </c>
       <c r="D35" s="44">
         <f>IFERROR(IF($D$31-$A35&lt;=0,"",$B$6/($D$31-$A35)/$B$11),"")</f>
-        <v>53.29610454111691</v>
+        <v>53.23737104748151</v>
       </c>
       <c r="E35" s="44">
         <f>IFERROR(IF($E$31-$A35&lt;=0,"",$B$6/($E$31-$A35)/$B$11),"")</f>
-        <v>50.24612589439541</v>
+        <v>50.193919048675085</v>
       </c>
       <c r="F35" s="28" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="70">
         <f>IFERROR($B$9*1.15,"")</f>
-        <v>23.589966099999994</v>
+        <v>23.551079999999995</v>
       </c>
       <c r="B36" s="44">
         <f>IFERROR(IF($B$31-$A36&lt;=0,"",$B$6/($B$31-$A36)/$B$11),"")</f>
-        <v>64.06512436926357</v>
+        <v>63.974365139656875</v>
       </c>
       <c r="C36" s="44">
         <f>IFERROR(IF($C$31-$A36&lt;=0,"",$B$6/($C$31-$A36)/$B$11),"")</f>
-        <v>59.70843953257839</v>
+        <v>59.62959696889497</v>
       </c>
       <c r="D36" s="44">
         <f>IFERROR(IF($D$31-$A36&lt;=0,"",$B$6/($D$31-$A36)/$B$11),"")</f>
-        <v>55.906569103360006</v>
+        <v>55.83744150098733</v>
       </c>
       <c r="E36" s="44">
         <f>IFERROR(IF($E$31-$A36&lt;=0,"",$B$6/($E$31-$A36)/$B$11),"")</f>
-        <v>52.55987575544575</v>
+        <v>52.49877218066325</v>
       </c>
       <c r="F36" s="28" t="n"/>
     </row>
@@ -5033,15 +5033,15 @@
       </c>
       <c r="B9" s="32">
         <f>IFERROR(IF(B8="","",B8*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>80504.55</v>
+        <v>77489.99999999999</v>
       </c>
       <c r="C9" s="32">
         <f>IFERROR(IF(C8="","",C8*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>114457.02449999998</v>
+        <v>110171.09999999999</v>
       </c>
       <c r="D9" s="32">
         <f>IFERROR(IF(D8="","",D8*'0. Supuestos'!$B$11*'0. Supuestos'!$B$13),"")</f>
-        <v>152958.645</v>
+        <v>147230.99999999997</v>
       </c>
       <c r="E9" s="28" t="n"/>
       <c r="F9" s="28" t="n"/>
@@ -5054,15 +5054,15 @@
       </c>
       <c r="B10" s="32">
         <f>IFERROR(IF(B8="","",B8*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>13062.420000000002</v>
+        <v>15876.000000000005</v>
       </c>
       <c r="C10" s="32">
         <f>IFERROR(IF(C8="","",C8*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>18571.443800000005</v>
+        <v>22571.64000000001</v>
       </c>
       <c r="D10" s="32">
         <f>IFERROR(IF(D8="","",D8*'0. Supuestos'!$B$12*'0. Supuestos'!$B$14),"")</f>
-        <v>24818.598000000005</v>
+        <v>30164.400000000012</v>
       </c>
       <c r="E10" s="28" t="n"/>
       <c r="F10" s="28" t="n"/>
@@ -5159,15 +5159,15 @@
       </c>
       <c r="B15" s="32">
         <f>IFERROR(IF(B8="","",SUM(B9:B14)),"")</f>
-        <v>121916.97</v>
+        <v>121715.99999999999</v>
       </c>
       <c r="C15" s="32">
         <f>IFERROR(IF(C8="","",SUM(C9:C14)),"")</f>
-        <v>173334.96829999998</v>
+        <v>173049.24</v>
       </c>
       <c r="D15" s="32">
         <f>IFERROR(IF(D8="","",SUM(D9:D14)),"")</f>
-        <v>231642.243</v>
+        <v>231260.4</v>
       </c>
       <c r="E15" s="28" t="n"/>
       <c r="F15" s="28" t="n"/>
@@ -5180,15 +5180,15 @@
       </c>
       <c r="B16" s="32">
         <f>IFERROR(IF(B8="","",B8-B15),"")</f>
-        <v>193083.03</v>
+        <v>193284.0</v>
       </c>
       <c r="C16" s="32">
         <f>IFERROR(IF(C8="","",C8-C15),"")</f>
-        <v>274515.03170000005</v>
+        <v>274800.76</v>
       </c>
       <c r="D16" s="32">
         <f>IFERROR(IF(D8="","",D8-D15),"")</f>
-        <v>366857.757</v>
+        <v>367239.6</v>
       </c>
       <c r="E16" s="28" t="n"/>
       <c r="F16" s="28" t="n"/>
@@ -5226,15 +5226,15 @@
       </c>
       <c r="B18" s="26">
         <f>IFERROR(IF(B8="","",B16-B17),"")</f>
-        <v>-35200.51000000001</v>
+        <v>-34999.54000000001</v>
       </c>
       <c r="C18" s="26">
         <f>IFERROR(IF(C8="","",C16-C17),"")</f>
-        <v>46231.49170000004</v>
+        <v>46517.22</v>
       </c>
       <c r="D18" s="26">
         <f>IFERROR(IF(D8="","",D16-D17),"")</f>
-        <v>138574.21699999998</v>
+        <v>138956.05999999997</v>
       </c>
       <c r="E18" s="28" t="n"/>
       <c r="F18" s="28" t="n"/>
@@ -5251,11 +5251,11 @@
       </c>
       <c r="C19" s="32">
         <f>IFERROR(IF(C8="","",MAX(0,C18-'0. Supuestos'!$B$42)*'0. Supuestos'!$B$37),"")</f>
-        <v>6934.723755000006</v>
+        <v>6977.583</v>
       </c>
       <c r="D19" s="32">
         <f>IFERROR(IF(D8="","",MAX(0,D18-'0. Supuestos'!$B$42)*'0. Supuestos'!$B$37),"")</f>
-        <v>20786.132549999995</v>
+        <v>20843.408999999996</v>
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
@@ -5272,15 +5272,15 @@
       </c>
       <c r="B20" s="26">
         <f>IFERROR(IF(B8="","",B18-B19),"")</f>
-        <v>-35200.51000000001</v>
+        <v>-34999.54000000001</v>
       </c>
       <c r="C20" s="26">
         <f>IFERROR(IF(C8="","",C18-C19),"")</f>
-        <v>39296.767945000036</v>
+        <v>39539.637</v>
       </c>
       <c r="D20" s="26">
         <f>IFERROR(IF(D8="","",D18-D19),"")</f>
-        <v>117788.08444999998</v>
+        <v>118112.65099999997</v>
       </c>
       <c r="E20" s="28" t="n"/>
       <c r="F20" s="28" t="n"/>
@@ -5293,15 +5293,15 @@
       </c>
       <c r="B21" s="44">
         <f>IFERROR(IF(B8="","",IF(B6-B15/(B5*B7)&lt;=0,"",B17/(B6-B15/(B5*B7))/B7)),"")</f>
-        <v>70.93845792662358</v>
+        <v>70.8646985782579</v>
       </c>
       <c r="C21" s="44">
         <f>IFERROR(IF(C8="","",IF(C6-C15/(C5*C7)&lt;=0,"",C17/(C6-C15/(C5*C7))/C7)),"")</f>
-        <v>54.05325168574366</v>
+        <v>53.99704898923861</v>
       </c>
       <c r="D21" s="44">
         <f>IFERROR(IF(D8="","",IF(D6-D15/(D5*D7)&lt;=0,"",D17/(D6-D15/(D5*D7))/D7)),"")</f>
-        <v>43.55870223564607</v>
+        <v>43.513411407702215</v>
       </c>
       <c r="E21" s="28" t="n"/>
       <c r="F21" s="28" t="n"/>
@@ -5376,15 +5376,15 @@
       </c>
       <c r="B25" s="26">
         <f>IFERROR(IF(B8="","",'Inversión Inicial'!$B$25+B20+'PyG 3 Años'!$B$36-'Financiación'!$B$45),"")</f>
-        <v>26627.249999999993</v>
+        <v>26828.219999999994</v>
       </c>
       <c r="C25" s="26">
         <f>IFERROR(IF(C8="","",'Inversión Inicial'!$B$25+C20+'PyG 3 Años'!$B$36-'Financiación'!$B$45),"")</f>
-        <v>101124.52794500004</v>
+        <v>101367.397</v>
       </c>
       <c r="D25" s="26">
         <f>IFERROR(IF(D8="","",'Inversión Inicial'!$B$25+D20+'PyG 3 Años'!$B$36-'Financiación'!$B$45),"")</f>
-        <v>179615.84444999998</v>
+        <v>179940.41099999996</v>
       </c>
       <c r="E25" s="25" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
       <c r="B26" s="28" t="n"/>
       <c r="C26" s="32">
         <f>IFERROR(IF(C8="","",'Tesorería 12 meses'!$M$22),"")</f>
-        <v>93173.37980435265</v>
+        <v>93243.88811842892</v>
       </c>
       <c r="D26" s="28" t="n"/>
       <c r="E26" s="28" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B18" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$B$53="","",'PyG 3 Años'!$B$53),"")</f>
-        <v>0.29703799999999997</v>
+        <v>0.2964</v>
       </c>
       <c r="C18" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$E$53="","",'PyG 3 Años'!$E$53),"")</f>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B21" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$B$56="","",'PyG 3 Años'!$B$56),"")</f>
-        <v>0.08774537891034953</v>
+        <v>0.08828767891034946</v>
       </c>
       <c r="C21" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$E$56="","",'PyG 3 Años'!$E$56),"")</f>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B22" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$B$51="","",'PyG 3 Años'!$B$51),"")</f>
-        <v>0.6129620000000001</v>
+        <v>0.6136</v>
       </c>
       <c r="C22" s="68">
         <f>IFERROR(IF('PyG 3 Años'!$E$51="","",'PyG 3 Años'!$E$51),"")</f>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B29" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$48="","",'PyG 3 Años'!$B$48),"")</f>
-        <v>39296.767945000036</v>
+        <v>39539.637</v>
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="n"/>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B30" s="44">
         <f>IFERROR(IF('Punto Equilibrio'!$B$15="","",'Punto Equilibrio'!$B$15),"")</f>
-        <v>54.05325168574366</v>
+        <v>53.99704898923861</v>
       </c>
       <c r="C30" s="28" t="n"/>
       <c r="D30" s="28" t="n"/>
@@ -7559,55 +7559,55 @@
       </c>
       <c r="B9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*B7*(1-MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>1963.5983748773563</v>
+        <v>1963.8018529997642</v>
       </c>
       <c r="C9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(C7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+B7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>12959.749274190552</v>
+        <v>12961.092229798445</v>
       </c>
       <c r="D9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(D7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+C7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>20269.690497029438</v>
+        <v>20271.790946193025</v>
       </c>
       <c r="E9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(E7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+D7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>28293.667492551</v>
+        <v>28296.59942731479</v>
       </c>
       <c r="F9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(F7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+E7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>35974.014772469025</v>
+        <v>35977.7425841616</v>
       </c>
       <c r="G9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(G7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+F7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>53351.860390133625</v>
+        <v>53357.388983209516</v>
       </c>
       <c r="H9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(H7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+G7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>61585.58539388072</v>
+        <v>61591.967207719885</v>
       </c>
       <c r="I9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(I7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+H7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>44627.2357926672</v>
+        <v>44631.8602954492</v>
       </c>
       <c r="J9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(J7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+I7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>32131.609770720377</v>
+        <v>32134.93941272342</v>
       </c>
       <c r="K9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(K7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+J7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>58015.40653046735</v>
+        <v>58021.418384083954</v>
       </c>
       <c r="L9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(L7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+K7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>50875.048803640595</v>
+        <v>50880.32073681208</v>
       </c>
       <c r="M9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",('PyG 3 Años'!$B$9+'PyG 3 Años'!$B$9*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11))*(M7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+L7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>41503.32928718049</v>
+        <v>41507.63007476775</v>
       </c>
       <c r="N9" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B9:M9)),"")</f>
-        <v>441550.7963798077</v>
+        <v>441596.5521352335</v>
       </c>
       <c r="O9" s="28" t="inlineStr">
         <is>
@@ -7648,51 +7648,51 @@
       </c>
       <c r="C11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(C7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+B7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-4684.213080846852</v>
+        <v>-4683.536907393926</v>
       </c>
       <c r="D11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(D7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+C7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-7494.740929354963</v>
+        <v>-7493.659051830283</v>
       </c>
       <c r="E11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(E7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+D7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-10880.149474148822</v>
+        <v>-10878.57890762862</v>
       </c>
       <c r="F11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(F7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+E7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-13094.50474873097</v>
+        <v>-13092.614536578476</v>
       </c>
       <c r="G11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(G7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+F7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-20344.389085223484</v>
+        <v>-20341.4523409768</v>
       </c>
       <c r="H11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(H7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+G7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-25550.25316825555</v>
+        <v>-25546.564949421416</v>
       </c>
       <c r="I11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(I7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+H7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-19162.689876191664</v>
+        <v>-19159.923712066062</v>
       </c>
       <c r="J11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(J7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+I7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-10645.93882010648</v>
+        <v>-10644.402062258923</v>
       </c>
       <c r="K11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(K7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+J7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-23421.065404234254</v>
+        <v>-23417.68453696963</v>
       </c>
       <c r="L11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(L7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+K7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-21291.87764021296</v>
+        <v>-21288.804124517847</v>
       </c>
       <c r="M11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",-('PyG 3 Años'!$B$13*(1+'PyG 3 Años'!$G$13)+'PyG 3 Años'!$B$14*(1+'PyG 3 Años'!$G$14)+'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$G$15)+'PyG 3 Años'!$B$16*(1+'PyG 3 Años'!$G$16)+'PyG 3 Años'!$B$17*(1+'PyG 3 Años'!$G$17)+'PyG 3 Años'!$B$18*(1+'PyG 3 Años'!$G$18))*(M7*(1-MIN(30,'0. Supuestos'!$B$59)/30)+L7*MIN(30,'0. Supuestos'!$B$59)/30)),"")</f>
-        <v>-14904.314348149072</v>
+        <v>-14902.162887162493</v>
       </c>
       <c r="N11" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B11:M11)),"")</f>
-        <v>-171474.13657545505</v>
+        <v>-171449.38401680448</v>
       </c>
       <c r="O11" s="28" t="str">
         <f>IFERROR("Materia prima, consumibles, comisiones e imprevistos, cada uno con SU tipo de IVA (la columna del P&amp;L) y con los días de pago a proveedor de Supuestos."&amp;IF('0. Supuestos'!$B$59=0,""," Con "&amp;TEXT('0. Supuestos'!$B$59,"0")&amp;" días de pago, las primeras compras se pagan ya en el año siguiente: la columna «Año» de esta fila recoge "&amp;TEXT(MAX(0,12-ROUNDUP('0. Supuestos'!$B$59/30,0)),"0")&amp;" mensualidades de compra, no el coste del ejercicio."),"")</f>
@@ -7955,59 +7955,59 @@
       </c>
       <c r="B16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*B7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>1076.2064278918347</v>
+        <v>1077.4272966262836</v>
       </c>
       <c r="C16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*C7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>1721.9302846269354</v>
+        <v>1723.8836746020538</v>
       </c>
       <c r="D16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*D7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>2499.7340211487617</v>
+        <v>2502.5697662546863</v>
       </c>
       <c r="E16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*E7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>3008.486150697629</v>
+        <v>3011.8990337507475</v>
       </c>
       <c r="F16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*F7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>4674.160190230218</v>
+        <v>4679.462645120064</v>
       </c>
       <c r="G16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*G7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>5870.216879410007</v>
+        <v>5876.876163416092</v>
       </c>
       <c r="H16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*H7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>4402.662659557505</v>
+        <v>4407.657122562069</v>
       </c>
       <c r="I16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*I7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>2445.92369975417</v>
+        <v>2448.6984014233717</v>
       </c>
       <c r="J16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*J7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>5381.032139459174</v>
+        <v>5387.136483131419</v>
       </c>
       <c r="K16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*K7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>4891.84739950834</v>
+        <v>4897.396802846743</v>
       </c>
       <c r="L16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*L7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>3424.2931796558373</v>
+        <v>3428.17776199272</v>
       </c>
       <c r="M16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$9*M7*SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)),"")</f>
-        <v>5625.62450943459</v>
+        <v>5632.006323273756</v>
       </c>
       <c r="N16" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B16:M16)),"")</f>
-        <v>45022.117541375</v>
+        <v>45073.191475</v>
       </c>
       <c r="O16" s="28" t="inlineStr">
         <is>
-          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en el servicio de catering, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); el alcohol que sale por drop-off, al general; el pan común y las harinas panificables, al superreducido (art. 91.Dos.1.1.º)</t>
+          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en el servicio de catering, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); el alcohol que sale por drop-off, al general; los servicios facturados aparte (mobiliario, carpas, decoración), al general (art. 90)</t>
         </is>
       </c>
     </row>
@@ -8019,55 +8019,55 @@
       </c>
       <c r="B17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*B7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>1411.447737390558</v>
+        <v>1417.6015988156682</v>
       </c>
       <c r="C17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*C7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>1735.9413798248927</v>
+        <v>1745.787558105069</v>
       </c>
       <c r="D17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*D7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>2126.8087218480687</v>
+        <v>2141.1024636127563</v>
       </c>
       <c r="E17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*E7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>2382.470379523605</v>
+        <v>2399.6732194165265</v>
       </c>
       <c r="F17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*F7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>3219.5164798939913</v>
+        <v>3246.24381894714</v>
       </c>
       <c r="G17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*G7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>3820.5672039484975</v>
+        <v>3854.1337208127347</v>
       </c>
       <c r="H17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*H7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>3083.0816529613735</v>
+        <v>3108.256540609551</v>
       </c>
       <c r="I17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*I7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>2099.767584978541</v>
+        <v>2113.7536336719727</v>
       </c>
       <c r="J17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*J7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>3574.73868695279</v>
+        <v>3605.5079940783403</v>
       </c>
       <c r="K17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*K7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>3328.9101699570815</v>
+        <v>3356.8822673439454</v>
       </c>
       <c r="L17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*L7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>2591.424618969957</v>
+        <v>2611.005087140762</v>
       </c>
       <c r="M17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$39*M7+'PyG 3 Años'!$B$40/12),"")</f>
-        <v>3697.652945450644</v>
+        <v>3729.8208574455375</v>
       </c>
       <c r="N17" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B17:M17)),"")</f>
-        <v>33072.3275617</v>
+        <v>33329.76876</v>
       </c>
       <c r="O17" s="28" t="inlineStr">
         <is>
@@ -8092,13 +8092,13 @@
       <c r="G18" s="28" t="n"/>
       <c r="H18" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",MAX(0,-E19)),"")</f>
-        <v>14651.127105395986</v>
+        <v>14675.41088305047</v>
       </c>
       <c r="I18" s="28" t="n"/>
       <c r="J18" s="28" t="n"/>
       <c r="K18" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",MAX(0,-H19)),"")</f>
-        <v>10520.817948424226</v>
+        <v>10607.223799939968</v>
       </c>
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="28" t="n"/>
@@ -8120,19 +8120,19 @@
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B16:D16)-SUM(B17:D17)-E18),"")</f>
-        <v>-14651.127105395986</v>
+        <v>-14675.41088305047</v>
       </c>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
       <c r="H19" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(E16:G16)-SUM(E17:G17)-H18),"")</f>
-        <v>-10520.817948424226</v>
+        <v>-10607.223799939968</v>
       </c>
       <c r="I19" s="28" t="n"/>
       <c r="J19" s="28" t="n"/>
       <c r="K19" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(H16:J16)-SUM(H17:J17)-K18),"")</f>
-        <v>-7048.787374546082</v>
+        <v>-7191.249961182972</v>
       </c>
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="28" t="n"/>
@@ -8188,55 +8188,55 @@
       </c>
       <c r="B21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B9:B15)+IF(B20="",0,B20)),"")</f>
-        <v>-15464.30329178931</v>
+        <v>-15464.099813666904</v>
       </c>
       <c r="C21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(C9:C15)+IF(C20="",0,C20)),"")</f>
-        <v>-9152.365473322967</v>
+        <v>-9150.34634426215</v>
       </c>
       <c r="D21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(D9:D15)+IF(D20="",0,D20)),"")</f>
-        <v>-4652.952098992192</v>
+        <v>-4649.769772303926</v>
       </c>
       <c r="E21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(E9:E15)+IF(E20="",0,E20)),"")</f>
-        <v>-14.38364826448742</v>
+        <v>-9.881146980496851</v>
       </c>
       <c r="F21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(F9:F15)+IF(F20="",0,F20)),"")</f>
-        <v>5451.608357071385</v>
+        <v>5457.226380916454</v>
       </c>
       <c r="G21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(G9:G15)+IF(G20="",0,G20)),"")</f>
-        <v>15579.569638243473</v>
+        <v>15588.034975566046</v>
       </c>
       <c r="H21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(H9:H15)+IF(H20="",0,H20)),"")</f>
-        <v>6980.570558958501</v>
+        <v>6990.6405916318</v>
       </c>
       <c r="I21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(I9:I15)+IF(I20="",0,I20)),"")</f>
-        <v>8036.644249808865</v>
+        <v>8044.034916716471</v>
       </c>
       <c r="J21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(J9:J15)+IF(J20="",0,J20)),"")</f>
-        <v>4057.7692839472293</v>
+        <v>4062.6356837978274</v>
       </c>
       <c r="K21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(K9:K15)+IF(K20="",0,K20)),"")</f>
-        <v>17166.439459566423</v>
+        <v>17175.832180447655</v>
       </c>
       <c r="L21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(L9:L15)+IF(L20="",0,L20)),"")</f>
-        <v>12155.269496760968</v>
+        <v>12163.614945627563</v>
       </c>
       <c r="M21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(M9:M15)+IF(M20="",0,M20)),"")</f>
-        <v>-2455.746727635251</v>
+        <v>-2449.294479061409</v>
       </c>
       <c r="N21" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B21:M21)),"")</f>
-        <v>37688.11980435264</v>
+        <v>37758.628118428926</v>
       </c>
       <c r="O21" s="28" t="n"/>
     </row>
@@ -8248,51 +8248,51 @@
       </c>
       <c r="B22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'Inversión Inicial'!$B$25+B21),"")</f>
-        <v>40020.956708210695</v>
+        <v>40021.1601863331</v>
       </c>
       <c r="C22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",B22+C21),"")</f>
-        <v>30868.59123488773</v>
+        <v>30870.81384207095</v>
       </c>
       <c r="D22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",C22+D21),"")</f>
-        <v>26215.639135895537</v>
+        <v>26221.044069767024</v>
       </c>
       <c r="E22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",D22+E21),"")</f>
-        <v>26201.25548763105</v>
+        <v>26211.162922786527</v>
       </c>
       <c r="F22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",E22+F21),"")</f>
-        <v>31652.863844702435</v>
+        <v>31668.38930370298</v>
       </c>
       <c r="G22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",F22+G21),"")</f>
-        <v>47232.43348294591</v>
+        <v>47256.42427926903</v>
       </c>
       <c r="H22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",G22+H21),"")</f>
-        <v>54213.00404190441</v>
+        <v>54247.064870900824</v>
       </c>
       <c r="I22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",H22+I21),"")</f>
-        <v>62249.648291713274</v>
+        <v>62291.09978761729</v>
       </c>
       <c r="J22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",I22+J21),"")</f>
-        <v>66307.41757566051</v>
+        <v>66353.73547141512</v>
       </c>
       <c r="K22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",J22+K21),"")</f>
-        <v>83473.85703522693</v>
+        <v>83529.56765186277</v>
       </c>
       <c r="L22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",K22+L21),"")</f>
-        <v>95629.1265319879</v>
+        <v>95693.18259749033</v>
       </c>
       <c r="M22" s="26">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",L22+M21),"")</f>
-        <v>93173.37980435265</v>
+        <v>93243.88811842892</v>
       </c>
       <c r="N22" s="28" t="n"/>
       <c r="O22" s="28" t="n"/>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="B23" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",IF(COUNT(B22:M22)=0,"",MIN(B22:M22))),"")</f>
-        <v>26201.25548763105</v>
+        <v>26211.162922786527</v>
       </c>
       <c r="C23" s="28" t="n"/>
       <c r="D23" s="28" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="B26" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$B$48+'PyG 3 Años'!$B$36+'Financiación'!$B$44),"")</f>
-        <v>52854.267945000036</v>
+        <v>53097.137</v>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="B27" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$C$48+'PyG 3 Años'!$C$36+'Financiación'!$B$46),"")</f>
-        <v>75754.80117840006</v>
+        <v>76026.81452000001</v>
       </c>
       <c r="C27" s="28" t="n"/>
       <c r="D27" s="28" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="B28" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'PyG 3 Años'!$D$48+'PyG 3 Años'!$D$36+'Financiación'!$B$48),"")</f>
-        <v>82068.08096104859</v>
+        <v>82327.29367480858</v>
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="B29" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",N21+'Financiación'!$B$44+'Financiación'!$B$45),"")</f>
-        <v>44903.11980435264</v>
+        <v>44973.628118428926</v>
       </c>
       <c r="C29" s="28" t="n"/>
       <c r="D29" s="28" t="inlineStr">
@@ -9825,11 +9825,11 @@
       </c>
       <c r="G27" s="70">
         <f>IFERROR(IF(E27="","",'PyG 3 Años'!$B$41-'PyG 3 Años'!$B$46+'PyG 3 Años'!$B$36+'PyG 3 Años'!$B$37),"")</f>
-        <v>52854.267945000036</v>
+        <v>53097.137</v>
       </c>
       <c r="H27" s="61">
         <f>IFERROR(IF(OR(E27="",E27=0),"",G27/E27),"")</f>
-        <v>7.3256088627858675</v>
+        <v>7.3592705474705475</v>
       </c>
     </row>
     <row r="28">
@@ -9858,11 +9858,11 @@
       </c>
       <c r="G28" s="70">
         <f>IFERROR(IF(E28="","",'PyG 3 Años'!$C$41-'PyG 3 Años'!$C$46+'PyG 3 Años'!$C$36+'PyG 3 Años'!$C$37),"")</f>
-        <v>75754.80117840006</v>
+        <v>76026.81452000001</v>
       </c>
       <c r="H28" s="61">
         <f>IFERROR(IF(OR(E28="",E28=0),"",G28/E28),"")</f>
-        <v>2.8361501765531267</v>
+        <v>2.8463339625944464</v>
       </c>
     </row>
     <row r="29">
@@ -9891,11 +9891,11 @@
       </c>
       <c r="G29" s="70">
         <f>IFERROR(IF(E29="","",'PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+'PyG 3 Años'!$D$37),"")</f>
-        <v>82068.08096104859</v>
+        <v>82327.29367480858</v>
       </c>
       <c r="H29" s="61">
         <f>IFERROR(IF(OR(E29="",E29=0),"",G29/E29),"")</f>
-        <v>3.072510239435759</v>
+        <v>3.0822147884869</v>
       </c>
     </row>
     <row r="30">
@@ -9924,11 +9924,11 @@
       </c>
       <c r="G30" s="70">
         <f>IFERROR(IF(E30="","",'PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+'PyG 3 Años'!$D$37),"")</f>
-        <v>82068.08096104859</v>
+        <v>82327.29367480858</v>
       </c>
       <c r="H30" s="61">
         <f>IFERROR(IF(OR(E30="",E30=0),"",G30/E30),"")</f>
-        <v>3.072510239435759</v>
+        <v>3.0822147884869</v>
       </c>
     </row>
     <row r="31">
@@ -9957,11 +9957,11 @@
       </c>
       <c r="G31" s="70">
         <f>IFERROR(IF(E31="","",'PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+'PyG 3 Años'!$D$37),"")</f>
-        <v>82068.08096104859</v>
+        <v>82327.29367480858</v>
       </c>
       <c r="H31" s="61">
         <f>IFERROR(IF(OR(E31="",E31=0),"",G31/E31),"")</f>
-        <v>3.072510239435759</v>
+        <v>3.0822147884869</v>
       </c>
     </row>
     <row r="32">
@@ -9990,11 +9990,11 @@
       </c>
       <c r="G32" s="70">
         <f>IFERROR(IF(E32="","",'PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+'PyG 3 Años'!$D$37),"")</f>
-        <v>82068.08096104859</v>
+        <v>82327.29367480858</v>
       </c>
       <c r="H32" s="61">
         <f>IFERROR(IF(OR(E32="",E32=0),"",G32/E32),"")</f>
-        <v>3.072510239435768</v>
+        <v>3.0822147884869087</v>
       </c>
     </row>
     <row r="33">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="B51" s="61">
         <f>IFERROR(('PyG 3 Años'!$B$41-'PyG 3 Años'!$B$46+'PyG 3 Años'!$B$36+B44)/(B44+B45),"")</f>
-        <v>7.3256088627858675</v>
+        <v>7.3592705474705475</v>
       </c>
       <c r="C51" s="28" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
       </c>
       <c r="B52" s="61">
         <f>IFERROR(('PyG 3 Años'!$C$41-'PyG 3 Años'!$C$46+'PyG 3 Años'!$C$36+B46)/(B46+B47),"")</f>
-        <v>2.8361501765531267</v>
+        <v>2.8463339625944464</v>
       </c>
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="28" t="n"/>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="B53" s="61">
         <f>IFERROR(('PyG 3 Años'!$D$41-'PyG 3 Años'!$D$46+'PyG 3 Años'!$D$36+B48)/(B48+B49),"")</f>
-        <v>3.072510239435759</v>
+        <v>3.0822147884869</v>
       </c>
       <c r="C53" s="28" t="n"/>
       <c r="D53" s="28" t="n"/>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="B54" s="62">
         <f>IFERROR(IF(COUNT(H27:H41)=0,"",MIN(H27:H41)),"")</f>
-        <v>2.8361501765531267</v>
+        <v>2.8463339625944464</v>
       </c>
       <c r="C54" s="25" t="inlineStr">
         <is>

--- a/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         <v>0.014421019833044477</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una "&amp;"compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier de menús y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina central, Cuota de la cocina central de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier de menús y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina "&amp;"central, Cuota de la cocina central de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier de menús y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina central, Cuota de la cocina central de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman 73285 € de los 130365 € de inversión.</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>

--- a/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
+++ b/astro-site/public/dl/plan-catering-tematico-eventos/plan-financiero-catering-tematico-eventos.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
         <v>0.014421019833044477</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una "&amp;"compra así sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de la furgoneta de este bloque (Furgoneta frigorífica usada con certificado ATP y Rotulación y estanterías de la furgoneta), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una compra así sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C28" s="28" t="n"/>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E28" s="28" t="n"/>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier de menús y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina central, Cuota de la cocina central de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier de menús y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina "&amp;"central, Cuota de la cocina central de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B26-B31-B32,"0")&amp;" € de los "&amp;TEXT(B26,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Marca, web, fotos, dossier de menús y lanzamiento, Constitución SL + notaría + registro, Declaración responsable, plan APPCC, alérgenos y formación, Stock inicial de producto, Fianza de la cocina central, Cuota de la cocina central de los meses previos al arranque ni Colchón operativo hasta alcanzar el equilibrio. Suman 73285 € de los 130365 € de inversión.</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
